--- a/AAII_Financials/Yearly/ENS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ENS_YR_FIN.xlsx
@@ -2972,7 +2972,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>55200</v>
+        <v>71300</v>
       </c>
       <c r="E58" s="3">
         <v>51100</v>
@@ -3023,7 +3023,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>116400</v>
+        <v>100300</v>
       </c>
       <c r="E59" s="3">
         <v>79000</v>
@@ -3125,10 +3125,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1134500</v>
+        <v>1188400</v>
       </c>
       <c r="E61" s="3">
-        <v>1151200</v>
+        <v>1184200</v>
       </c>
       <c r="F61" s="3">
         <v>883500</v>
@@ -3176,10 +3176,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>114300</v>
+        <v>60400</v>
       </c>
       <c r="E62" s="3">
-        <v>79800</v>
+        <v>46800</v>
       </c>
       <c r="F62" s="3">
         <v>44600</v>
